--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffKingdee.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffKingdee.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>核对周期</t>
   </si>
@@ -53,9 +53,6 @@
     <t>本月期初</t>
   </si>
   <si>
-    <t>平台本月期末</t>
-  </si>
-  <si>
     <t>本期-入库</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
     <t>{.kingdeeInitQty}</t>
   </si>
   <si>
-    <t>{.platformClosingQty}</t>
-  </si>
-  <si>
     <t>{.kingdeeInstockQty}</t>
   </si>
   <si>
@@ -128,22 +122,22 @@
     <t>{.kingdeeClosingQty}</t>
   </si>
   <si>
+    <t>{.kingdeeClosingIntransitQty}</t>
+  </si>
+  <si>
+    <t>{.finishStatusName}</t>
+  </si>
+  <si>
+    <t>{.diffClosingQty}</t>
+  </si>
+  <si>
+    <t>{.diffClosingIntransitQty}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
     <t>{.createTime}</t>
-  </si>
-  <si>
-    <t>{.finishStatusName}</t>
-  </si>
-  <si>
-    <t>{.kingdeeClosingIntransitQty}</t>
-  </si>
-  <si>
-    <t>{.diffClosingQty}</t>
-  </si>
-  <si>
-    <t>{.diffClosingIntransitQty}</t>
-  </si>
-  <si>
-    <t>{.remark}</t>
   </si>
   <si>
     <t>{.finishTime}</t>
@@ -1336,13 +1330,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="21" width="30" customWidth="1"/>
+    <col min="1" max="20" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:21">
+    <row r="1" ht="15" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1403,73 +1397,67 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>30</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>32</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
         <v>33</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>34</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>35</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" t="s">
         <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T2" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffKingdee.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffKingdee.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25395" windowHeight="7095"/>
   </bookViews>
   <sheets>
     <sheet name="金蝶库存差异" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>核对周期</t>
   </si>
@@ -125,19 +125,25 @@
     <t>{.kingdeeClosingIntransitQty}</t>
   </si>
   <si>
+    <t>{.closingQty}</t>
+  </si>
+  <si>
+    <t>{.intransitQty}</t>
+  </si>
+  <si>
+    <t>{.diffClosingQty}</t>
+  </si>
+  <si>
+    <t>{.diffClosingIntransitQty}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
+  </si>
+  <si>
     <t>{.finishStatusName}</t>
-  </si>
-  <si>
-    <t>{.diffClosingQty}</t>
-  </si>
-  <si>
-    <t>{.diffClosingIntransitQty}</t>
-  </si>
-  <si>
-    <t>{.remark}</t>
-  </si>
-  <si>
-    <t>{.createTime}</t>
   </si>
   <si>
     <t>{.finishTime}</t>
@@ -1439,25 +1445,25 @@
         <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffKingdee.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpInventoryDiffKingdee.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25395" windowHeight="7095"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="金蝶库存差异" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
     <t>{.checkMonth}</t>
   </si>
   <si>
-    <t>{.warehouseName}</t>
+    <t>{.checkPlatformName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
